--- a/static/standards-correlations/West_Virginia_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/West_Virginia_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$18</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Policy 2520.14 (126CSR44N) - CS becomes a graduation requirement for Grade 9 entrants in 2027-28</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Policy 2520.14 (126CSR44N) - CS becomes a graduation requirement for Grade 9 entrants in 2027-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -741,7 +742,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Both halves are present but optional. RELIABLE: Ext 5.3F (Talking to a Server) traces a file from the student's own machine across the internet to a remote server and asks what has to go right for it to arrive - address routing, server uptime, the local connection. SAFE: Ext 5.3G (Secret Messages / HTTPS) covers why the s in HTTPS matters and the risk of sending a password over plain HTTP. Discovery Systems 9 covers senders, receivers, and protocols. Neither Extension is in the core flow, and no lab analyses transmission methods against one another.</t>
+          <t>Both halves are present but optional. RELIABLE: Ext 5.3F (Talking to a Server) traces a file from the student's own machine across the internet to a remote server and asks what has to go right for it to arrive - address routing, server uptime, the local connection. SAFE: Ext 5.3G (Secret Messages / HTTPS) covers why the s in HTTPS matters and the risk of sending a password over plain HTTP. Introductory Systems 9 covers senders, receivers, and protocols. Neither Extension is in the core flow, and no lab analyses transmission methods against one another.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1066,7 @@
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>NOT ADDRESSED. Cybercrime, its cost, and its national or global economic impact appear nowhere in either track or in the Discovery projects, and there is no adjacent evidence to cite. This is the only blank in the West Virginia file. Given that cybersecurity is half the title of West Virginia's standards document, a district should be told plainly that this standard requires supplementation - see the note on West Virginia's cybersecurity emphasis in Source and Attribution.</t>
+          <t>NOT ADDRESSED. Cybercrime, its cost, and its national or global economic impact appear nowhere in either track or in the Introductory projects, and there is no adjacent evidence to cite. This is the only blank in the West Virginia file. Given that cybersecurity is half the title of West Virginia's standards document, a district should be told plainly that this standard requires supplementation - see the note on West Virginia's cybersecurity emphasis in Source and Attribution.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1109,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>West Virginia asks for BOTH signs and the curriculum supplies both in core. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app routing a driver into a wall and Unit 1.4 a delivery app whose stored model has drifted from reality - negative impacts of systems that are useful. Ext 4.2E (A Basic Building Block of AI) identifies the sense-compare-adjust loop the student wrote as a building block inside self-driving cars and stabilising drones, which is the positive case. Discovery Systems 12 asks whose responsibility it is to anticipate harm from a genuinely useful invention, and Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a real deployed system should exist.</t>
+          <t>West Virginia asks for BOTH signs and the curriculum supplies both in core. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app routing a driver into a wall and Unit 1.4 a delivery app whose stored model has drifted from reality - negative impacts of systems that are useful. Ext 4.2E (A Basic Building Block of AI) identifies the sense-compare-adjust loop the student wrote as a building block inside self-driving cars and stabilising drones, which is the positive case. Introductory Systems 12 asks whose responsibility it is to anticipate harm from a genuinely useful invention, and Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a real deployed system should exist.</t>
         </is>
       </c>
     </row>
@@ -1228,6 +1229,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1272,7 +1274,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1286,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1420,6 +1422,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -1446,7 +1450,7 @@
 CYBERSECURITY EMPHASIS: West Virginia titles its standards for Technology AND Computer Science and names one cluster Networks and CYBER INFRASTRUCTURE. Cybersecurity content is lighter at 9-12 than the 2019 framing suggested - only CS.9-12.3, CS.9-12.4, and CS.9-12.11 touch it directly - but CS.9-12.11 (economic impact of cybercrime) is the one blank in this file and should be disclosed rather than glossed.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT: 7 Full, 6 Partial, 1 blank of 14. Touched 13 of 14.
   Cluster 4 Programming and Algorithms          3 Full of 3   - complete
